--- a/publication/web-root/cibmtr-reporting/StructureDefinition-cibmtr-medication-request.xlsx
+++ b/publication/web-root/cibmtr-reporting/StructureDefinition-cibmtr-medication-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T11:11:22-05:00</t>
+    <t>2023-05-04T21:49:21-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2525,15 +2525,15 @@
   <dimension ref="A1:AO101"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="60.2578125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="60.2578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="18.1875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="38.81640625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.8984375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.69921875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.07421875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.625" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.98828125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="59.296875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="59.296875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="17.765625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="38.4609375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="6.1484375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.58203125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.94140625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="14.7109375" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="12.1875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2544,27 +2544,27 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="8.84375" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.7109375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.0859375" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.078125" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.30859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="192.3984375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="70.6171875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.69140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.73046875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="40.0390625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="14.984375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="12.30078125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="58.46875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.5" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.875" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="9.04296875" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="15.77734375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="16.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="17.40234375" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.9609375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="191.95703125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="70.62109375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.8828125" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="20.84375" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="40.0859375" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="15.703125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="13.125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="57.07421875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.53125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.890625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="26.71484375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="26.69140625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="32.84375" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="125.8203125" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="33.05078125" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="131.0546875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/publication/web-root/cibmtr-reporting/StructureDefinition-cibmtr-medication-request.xlsx
+++ b/publication/web-root/cibmtr-reporting/StructureDefinition-cibmtr-medication-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T21:49:21-05:00</t>
+    <t>2023-05-05T10:50:04-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/publication/web-root/cibmtr-reporting/StructureDefinition-cibmtr-medication-request.xlsx
+++ b/publication/web-root/cibmtr-reporting/StructureDefinition-cibmtr-medication-request.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.8</t>
+    <t>0.1.9</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T16:25:42-06:00</t>
+    <t>2025-09-19T15:08:00-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2543,17 +2543,17 @@
   <dimension ref="A1:AO101"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="60.2578125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="60.2578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="18.18359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="38.81640625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.90234375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.69921875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.07421875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.625" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.98828125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="54.0390625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="54.0390625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="16.30859375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.8125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.21484375" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.55078125" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="243.55859375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2562,27 +2562,27 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="8.84375" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.71484375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.08984375" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.078125" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.3125" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="192.3984375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="70.6171875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.69140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.73046875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="40.0390625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="14.98828125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="12.3046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="58.46484375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.5" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.87890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="7.93359375" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.08984375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="14.4296875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="172.55078125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="63.33203125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="35.90625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.44140625" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.03515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="52.43359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.51953125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.859375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="26.71875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="23.9609375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="32.84375" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="125.8203125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="248.7734375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="29.45703125" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="112.83984375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/publication/web-root/cibmtr-reporting/StructureDefinition-cibmtr-medication-request.xlsx
+++ b/publication/web-root/cibmtr-reporting/StructureDefinition-cibmtr-medication-request.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.9</t>
+    <t>0.1.10</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-19T15:08:00-05:00</t>
+    <t>2026-04-23T10:10:52-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -443,7 +443,7 @@
     <t>MedicationRequest.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -481,7 +481,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">pattern:system}
@@ -671,7 +671,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -3874,7 +3874,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>153</v>
       </c>
@@ -5512,7 +5512,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>246</v>
       </c>
@@ -5629,7 +5629,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
         <v>252</v>
       </c>
@@ -5982,7 +5982,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
         <v>272</v>
       </c>
@@ -6216,7 +6216,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
         <v>292</v>
       </c>
@@ -6333,7 +6333,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
         <v>301</v>
       </c>
@@ -6682,7 +6682,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
         <v>322</v>
       </c>
@@ -6797,7 +6797,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
         <v>327</v>
       </c>
@@ -6912,7 +6912,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
         <v>338</v>
       </c>
@@ -7029,7 +7029,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
         <v>348</v>
       </c>
@@ -7261,7 +7261,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
         <v>363</v>
       </c>
@@ -7376,7 +7376,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
         <v>372</v>
       </c>
@@ -7838,7 +7838,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
         <v>399</v>
       </c>
@@ -7953,7 +7953,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
         <v>409</v>
       </c>
@@ -8879,7 +8879,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
         <v>457</v>
       </c>
@@ -9464,7 +9464,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
         <v>479</v>
       </c>
@@ -14374,12 +14374,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AO101">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/publication/web-root/cibmtr-reporting/StructureDefinition-cibmtr-medication-request.xlsx
+++ b/publication/web-root/cibmtr-reporting/StructureDefinition-cibmtr-medication-request.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$102</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3761" uniqueCount="706">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3797" uniqueCount="711">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.9</t>
+    <t>0.1.11</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-19T15:08:00-05:00</t>
+    <t>2026-06-10T07:35:08-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -269,11 +269,13 @@
     <t>Ordering of medication for patient or group</t>
   </si>
   <si>
-    <t>The US Core Medication Request (Order) Profile is based upon the core FHIR MedicationRequest Resource and created to meet the 2015 Edition Common Clinical Data Set 'Medications' requirements.</t>
+    <t>\-</t>
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}mcode-reason-required:One of reasonCode or reasonReference SHALL be present {reasonCode.exists() or reasonReference.exists()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}us-core-21:requester SHALL be present if intent is "order" {(intent='order' or intent='original-order' or intent='reflex-order'or intent='filler-order' or intent='instance-order') implies requester.exists()}mcode-reason-required:One of reasonCode or reasonReference SHALL be present {reasonCode.exists() or reasonReference.exists()}termination-reason-code-invariant:When status is stopped, only certain statusReason values are allowed {status = 'stopped' and statusReason.exists() and statusReason.coding.exists() implies statusReason.coding.exists(system = 'http://snomed.info/sct' and (code = '182992009' or code = '266721009' or code = '407563006' or code = '160932005' or code = '105480006' or code = '184081006' or code = '309846006' or code = '399307001' or code = '419620001' or code = '7058009' or code = '443729008' or code = '77386006'))}termination-reason-invariant:Certain statusReason values are allowed only when status is stopped {statusReason.exists() and statusReason.coding.exists(
+      system = 'http://snomed.info/sct' and (code = '182992009' or code = '266721009' or code = '407563006' or code = '160932005' or
+ code = '105480006' or code = '184081006' or code = '309846006' or code = '399307001' or  code = '419620001' or code = '7058009' or code = '443729008' or code = '77386006')) implies status = 'stopped'}</t>
   </si>
   <si>
     <t>Request</t>
@@ -443,7 +445,7 @@
     <t>MedicationRequest.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -481,7 +483,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">pattern:system}
@@ -671,7 +673,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -800,20 +802,20 @@
 </t>
   </si>
   <si>
-    <t>MedicationRequest.extension:terminationReason</t>
-  </si>
-  <si>
-    <t>terminationReason</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://hl7.org/fhir/us/mcode/StructureDefinition/mcode-treatment-termination-reason}
+    <t>MedicationRequest.extension:normalizationBasis</t>
+  </si>
+  <si>
+    <t>normalizationBasis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/us/mcode/StructureDefinition/mcode-normalization-basis}
 </t>
   </si>
   <si>
-    <t>Treatment Termination Reason Extension</t>
-  </si>
-  <si>
-    <t>A code explaining the unplanned or premature termination, or normal completion, of a plan of treatment, course of medication, or research study.</t>
+    <t>Normalization Basis Extension</t>
+  </si>
+  <si>
+    <t>The method (e.g., body weight, body surface area, flat dose, age) used to normalize the medication dosage.</t>
   </si>
   <si>
     <t>MedicationRequest.modifierExtension</t>
@@ -866,7 +868,7 @@
     <t>MedicationRequest.status</t>
   </si>
   <si>
-    <t>active | on-hold | cancelled | completed | entered-in-error | stopped | draft | unknown</t>
+    <t>(USCDI) active | on-hold | cancelled | completed | entered-in-error | stopped | draft | unknown</t>
   </si>
   <si>
     <t>A code specifying the current state of the order.  Generally, this will be active or completed state.</t>
@@ -912,10 +914,7 @@
     <t>This is generally only used for "exception" statuses such as "suspended" or "cancelled". The reason why the MedicationRequest was created at all is captured in reasonCode, not here.</t>
   </si>
   <si>
-    <t>Identifies the reasons for a given status.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationrequest-status-reason</t>
+    <t>http://hl7.org/fhir/us/mcode/ValueSet/mcode-treatment-termination-reason-vs</t>
   </si>
   <si>
     <t>Request.statusReason</t>
@@ -927,7 +926,7 @@
     <t>MedicationRequest.intent</t>
   </si>
   <si>
-    <t>proposal | plan | order | original-order | reflex-order | filler-order | instance-order | option</t>
+    <t>(USCDI) proposal | plan | order | original-order | reflex-order | filler-order | instance-order | option</t>
   </si>
   <si>
     <t>Whether the request is a proposal, plan, or an original order.</t>
@@ -946,6 +945,10 @@
     <t>http://hl7.org/fhir/ValueSet/medicationrequest-intent</t>
   </si>
   <si>
+    <t xml:space="preserve">us-core-21
+</t>
+  </si>
+  <si>
     <t>Request.intent</t>
   </si>
   <si>
@@ -958,7 +961,7 @@
     <t>MedicationRequest.category</t>
   </si>
   <si>
-    <t>Type of medication usage</t>
+    <t>(USCDI) Type of medication usage</t>
   </si>
   <si>
     <t>Indicates the type of medication request (for example, where the medication is expected to be consumed or administered (i.e. inpatient or outpatient)).</t>
@@ -967,10 +970,14 @@
     <t>The category can be used to include where the medication is expected to be consumed or other types of requests.</t>
   </si>
   <si>
-    <t>The type of medication order.</t>
+    <t>A coded concept identifying the category of medication request.  For example, where the medication is to be consumed or administered, or the type of medication treatment.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/medicationrequest-category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
   </si>
   <si>
     <t>Message/Body/NewRx/MedicationPrescribed/Directions@@ -983,6 +990,15 @@
     <t>.inboundRelationship[typeCode=COMP].source[classCode=OBS, moodCode=EVN, code="type of medication usage"].value</t>
   </si>
   <si>
+    <t>MedicationRequest.category:us-core</t>
+  </si>
+  <si>
+    <t>us-core</t>
+  </si>
+  <si>
+    <t>The type of medication order. Note that other codes are permitted, see [Required Bindings When Slicing by Value Sets](http://hl7.org/fhir/us/core/general-requirements.html#required-bindings-when-slicing-by-valuesets)</t>
+  </si>
+  <si>
     <t>MedicationRequest.priority</t>
   </si>
   <si>
@@ -1026,10 +1042,10 @@
   </si>
   <si>
     <t>boolean
-Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitioner|http://hl7.org/fhir/us/core/StructureDefinition/us-core-organization|http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient|http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitionerrole|RelatedPerson)</t>
-  </si>
-  <si>
-    <t>Reported rather than primary record</t>
+Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitioner|http://hl7.org/fhir/us/core/StructureDefinition/us-core-organization|http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient|http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitionerrole|http://hl7.org/fhir/us/core/StructureDefinition/us-core-relatedperson)</t>
+  </si>
+  <si>
+    <t>(USCDI) Reported rather than primary record</t>
   </si>
   <si>
     <t>Indicates if this record was captured as a secondary 'reported' record rather than as an original primary source-of-truth record.  It may also indicate the source of the report.</t>
@@ -1045,7 +1061,7 @@
 Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-medication)</t>
   </si>
   <si>
-    <t>Medication to be taken</t>
+    <t>(USCDI) Medication to be taken</t>
   </si>
   <si>
     <t>Identifies the medication being requested. This is a link to a resource that represents the medication which may be the details of the medication or simply an attribute carrying a code that identifies the medication from a known list of medications.</t>
@@ -1085,7 +1101,7 @@
 </t>
   </si>
   <si>
-    <t>Who or group medication request is for</t>
+    <t>(USCDI) Who or group medication request is for</t>
   </si>
   <si>
     <t>The patient receiving the medication.</t>
@@ -1118,7 +1134,7 @@
 </t>
   </si>
   <si>
-    <t>Encounter created as part of encounter/admission/stay</t>
+    <t>(USCDI) Encounter created as part of encounter/admission/stay</t>
   </si>
   <si>
     <t>The Encounter during which this [x] was created or to which the creation of this record is tightly associated.</t>
@@ -1165,7 +1181,7 @@
 </t>
   </si>
   <si>
-    <t>When request was initially authored</t>
+    <t>(USCDI) When request was initially authored</t>
   </si>
   <si>
     <t>The date (and perhaps time) when the prescription was initially written or authored on.</t>
@@ -1193,7 +1209,7 @@
 </t>
   </si>
   <si>
-    <t>Who/What requested the Request</t>
+    <t>(USCDI) Who/What requested the Request</t>
   </si>
   <si>
     <t>The individual, organization, or device that initiated the request and has responsibility for its activation.</t>
@@ -1273,7 +1289,7 @@
     <t>MedicationRequest.reasonCode</t>
   </si>
   <si>
-    <t>Reason or indication for ordering or not ordering the medication</t>
+    <t>(USCDI) Reason or indication for ordering or not ordering the medication</t>
   </si>
   <si>
     <t>The reason or the indication for ordering or not ordering the medication.</t>
@@ -1303,11 +1319,11 @@
     <t>MedicationRequest.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/mcode/StructureDefinition/mcode-primary-cancer-condition|http://hl7.org/fhir/us/mcode/StructureDefinition/mcode-secondary-cancer-condition)
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-condition-problems-health-concerns)
 </t>
   </si>
   <si>
-    <t>Condition or observation that supports why the prescription is being written</t>
+    <t>(USCDI) US Core Condition or Observation that supports the prescription</t>
   </si>
   <si>
     <t>Condition or observation that supports why the medication was ordered.</t>
@@ -1456,7 +1472,7 @@
 </t>
   </si>
   <si>
-    <t>How the medication should be taken</t>
+    <t>(USCDI) How the medication should be taken</t>
   </si>
   <si>
     <t>Indicates how the medication is to be used by the patient.</t>
@@ -1522,7 +1538,7 @@
     <t>MedicationRequest.dosageInstruction.text</t>
   </si>
   <si>
-    <t>Free text dosage instructions e.g. SIG</t>
+    <t>(USCDI) Free text dosage instructions e.g. SIG</t>
   </si>
   <si>
     <t>Free text dosage instructions e.g. SIG.</t>
@@ -1583,7 +1599,7 @@
 </t>
   </si>
   <si>
-    <t>When medication should be administered</t>
+    <t>(USCDI) When medication should be administered</t>
   </si>
   <si>
     <t>When medication should be administered.</t>
@@ -1726,7 +1742,7 @@
 </t>
   </si>
   <si>
-    <t>Amount of medication administered</t>
+    <t>(USCDI) Amount of medication administered</t>
   </si>
   <si>
     <t>The amount of medication administered.</t>
@@ -1771,11 +1787,11 @@
     <t>MedicationRequest.dosageInstruction.doseAndRate.dose[x]</t>
   </si>
   <si>
-    <t>Range
-Quantity {SimpleQuantity}</t>
-  </si>
-  <si>
-    <t>Amount of medication per dose</t>
+    <t>Quantity
+Range</t>
+  </si>
+  <si>
+    <t>(USCDI) Amount of medication per dose</t>
   </si>
   <si>
     <t>Amount of medication per dose.</t>
@@ -1785,6 +1801,9 @@
   </si>
   <si>
     <t>The amount of therapeutic or other substance given at one administration event.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/ucum-common</t>
   </si>
   <si>
     <t>Dosage.doseAndRate.dose[x]</t>
@@ -1898,7 +1917,7 @@
 </t>
   </si>
   <si>
-    <t>Medication supply authorization</t>
+    <t>(USCDI) Medication supply authorization</t>
   </si>
   <si>
     <t>Indicates the specific details for the dispense or medication supply part of a medication request (also known as a Medication Prescription or Medication Order).  Note that this information is not always sent with the order.  There may be in some settings (e.g. hospitals) institutional or system support for completing the dispense details in the pharmacy department.</t>
@@ -2012,7 +2031,7 @@
 </t>
   </si>
   <si>
-    <t>Number of refills authorized</t>
+    <t>(USCDI) Number of refills authorized</t>
   </si>
   <si>
     <t>An integer indicating the number of times, in addition to the original dispense, (aka refills or repeats) that the patient can receive the prescribed medication. Usage Notes: This integer does not include the original order dispense. This means that if an order indicates dispense 30 tablets plus "3 repeats", then the order can be dispensed a total of 4 times and the patient can receive a total of 120 tablets.  A prescriber may explicitly say that zero refills are permitted after the initial dispense.</t>
@@ -2033,7 +2052,7 @@
     <t>MedicationRequest.dispenseRequest.quantity</t>
   </si>
   <si>
-    <t>Amount of medication to supply per dispense</t>
+    <t>(USCDI) Amount of medication to supply per dispense</t>
   </si>
   <si>
     <t>The amount that is to be dispensed for one fill.</t>
@@ -2540,12 +2559,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO101"/>
+  <dimension ref="A1:AO102"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="54.0390625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="54.0390625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="16.30859375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="16.05078125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.8125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.21484375" customWidth="true" bestFit="true"/>
@@ -2553,7 +2572,7 @@
     <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="243.55859375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2567,8 +2586,8 @@
     <col min="22" max="22" width="14.4296875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="172.55078125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="63.33203125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="177.9765625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="65.70703125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="35.90625" customWidth="true" bestFit="true"/>
@@ -2746,7 +2765,9 @@
       <c r="M2" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="N2" s="2"/>
+      <c r="N2" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
         <v>21</v>
@@ -3874,7 +3895,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>153</v>
       </c>
@@ -5512,7 +5533,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>246</v>
       </c>
@@ -5647,10 +5668,10 @@
         <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>21</v>
@@ -5982,7 +6003,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
         <v>272</v>
       </c>
@@ -6099,7 +6120,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
         <v>283</v>
       </c>
@@ -6118,7 +6139,7 @@
         <v>89</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>21</v>
@@ -6162,13 +6183,11 @@
         <v>21</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="Y31" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="Y31" s="2"/>
+      <c r="Z31" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="Z31" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>21</v>
@@ -6201,27 +6220,27 @@
         <v>101</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM31" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AL31" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM31" t="s" s="2">
+      <c r="AN31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO31" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="AN31" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="32" hidden="true">
-      <c r="A32" t="s" s="2">
-        <v>292</v>
-      </c>
       <c r="B32" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6247,13 +6266,13 @@
         <v>179</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6282,11 +6301,11 @@
         <v>276</v>
       </c>
       <c r="Y32" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="Z32" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="Z32" t="s" s="2">
-        <v>297</v>
-      </c>
       <c r="AA32" t="s" s="2">
         <v>21</v>
       </c>
@@ -6303,7 +6322,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>89</v>
@@ -6312,7 +6331,7 @@
         <v>89</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>21</v>
+        <v>297</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>101</v>
@@ -6396,7 +6415,7 @@
         <v>21</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="Y33" t="s" s="2">
         <v>305</v>
@@ -6408,16 +6427,14 @@
         <v>21</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>307</v>
+      </c>
+      <c r="AC33" s="2"/>
       <c r="AD33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="AF33" t="s" s="2">
         <v>301</v>
@@ -6438,10 +6455,10 @@
         <v>21</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>300</v>
@@ -6450,14 +6467,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="C34" s="2"/>
+        <v>301</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>311</v>
+      </c>
       <c r="D34" t="s" s="2">
         <v>21</v>
       </c>
@@ -6466,27 +6485,29 @@
         <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>179</v>
+        <v>284</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>21</v>
@@ -6517,7 +6538,7 @@
         <v>312</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>21</v>
@@ -6535,13 +6556,13 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>21</v>
@@ -6550,16 +6571,16 @@
         <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>314</v>
+        <v>21</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>21</v>
+        <v>308</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>316</v>
+        <v>300</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>21</v>
@@ -6567,10 +6588,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6587,23 +6608,21 @@
         <v>21</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="J35" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>320</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>21</v>
@@ -6628,13 +6647,13 @@
         <v>21</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>21</v>
+        <v>276</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>21</v>
+        <v>316</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>21</v>
+        <v>317</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>21</v>
@@ -6652,7 +6671,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6667,16 +6686,16 @@
         <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>21</v>
+        <v>318</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>21</v>
+        <v>320</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>21</v>
@@ -6684,10 +6703,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6701,24 +6720,26 @@
         <v>89</v>
       </c>
       <c r="H36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I36" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="I36" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="J36" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="M36" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>21</v>
@@ -6767,7 +6788,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6788,21 +6809,21 @@
         <v>21</v>
       </c>
       <c r="AM36" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AN36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO36" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="AN36" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO36" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="37" hidden="true">
-      <c r="A37" t="s" s="2">
-        <v>327</v>
-      </c>
       <c r="B37" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6810,7 +6831,7 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>89</v>
@@ -6825,17 +6846,15 @@
         <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="M37" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>331</v>
-      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>21</v>
@@ -6860,11 +6879,13 @@
         <v>21</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="Y37" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z37" t="s" s="2">
-        <v>332</v>
+        <v>21</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>21</v>
@@ -6882,10 +6903,10 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH37" t="s" s="2">
         <v>89</v>
@@ -6897,27 +6918,27 @@
         <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>333</v>
+        <v>21</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>334</v>
+        <v>21</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>336</v>
+        <v>21</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>337</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6940,16 +6961,16 @@
         <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6975,13 +6996,11 @@
         <v>21</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y38" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>21</v>
+        <v>336</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>21</v>
@@ -6999,7 +7018,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>89</v>
@@ -7014,27 +7033,27 @@
         <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7042,7 +7061,7 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>89</v>
@@ -7054,19 +7073,19 @@
         <v>21</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7116,10 +7135,10 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>89</v>
@@ -7131,27 +7150,27 @@
         <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>280</v>
+        <v>348</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>356</v>
+        <v>351</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7162,10 +7181,10 @@
         <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>21</v>
@@ -7174,15 +7193,17 @@
         <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>355</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>356</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>21</v>
@@ -7231,13 +7252,13 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>21</v>
@@ -7246,27 +7267,27 @@
         <v>101</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>21</v>
+        <v>280</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>21</v>
+        <v>360</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7277,25 +7298,25 @@
         <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="L41" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7346,13 +7367,13 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>21</v>
@@ -7361,27 +7382,27 @@
         <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AN41" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="AO41" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="AL41" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="AO41" t="s" s="2">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="42" hidden="true">
-      <c r="A42" t="s" s="2">
-        <v>372</v>
-      </c>
       <c r="B42" t="s" s="2">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7404,13 +7425,13 @@
         <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7461,7 +7482,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -7476,27 +7497,27 @@
         <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AO42" t="s" s="2">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="AL42" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="43" hidden="true">
-      <c r="A43" t="s" s="2">
-        <v>378</v>
-      </c>
       <c r="B43" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7510,22 +7531,22 @@
         <v>89</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="L43" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7576,7 +7597,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -7585,22 +7606,22 @@
         <v>89</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>21</v>
+        <v>297</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>383</v>
+        <v>349</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>21</v>
@@ -7608,10 +7629,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7631,20 +7652,18 @@
         <v>21</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>284</v>
+        <v>383</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>388</v>
-      </c>
+        <v>385</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>21</v>
@@ -7669,13 +7688,13 @@
         <v>21</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>209</v>
+        <v>21</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>389</v>
+        <v>21</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>390</v>
+        <v>21</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>21</v>
@@ -7693,7 +7712,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7708,16 +7727,16 @@
         <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>21</v>
+        <v>388</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>21</v>
@@ -7725,10 +7744,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7748,18 +7767,20 @@
         <v>21</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>394</v>
+        <v>284</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>391</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>392</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>21</v>
@@ -7784,13 +7805,13 @@
         <v>21</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>21</v>
+        <v>209</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>21</v>
+        <v>393</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>21</v>
+        <v>394</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>21</v>
@@ -7808,7 +7829,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7823,16 +7844,16 @@
         <v>101</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>21</v>
+        <v>395</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>398</v>
+        <v>21</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>21</v>
@@ -7840,10 +7861,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7854,10 +7875,10 @@
         <v>79</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>21</v>
@@ -7866,17 +7887,15 @@
         <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>284</v>
+        <v>398</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="M46" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>402</v>
-      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>21</v>
@@ -7901,11 +7920,13 @@
         <v>21</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="Y46" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z46" t="s" s="2">
-        <v>403</v>
+        <v>21</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>21</v>
@@ -7923,13 +7944,13 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>21</v>
@@ -7938,27 +7959,27 @@
         <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>404</v>
+        <v>21</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>405</v>
+        <v>21</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>408</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7981,16 +8002,16 @@
         <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>410</v>
+        <v>284</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8016,13 +8037,11 @@
         <v>21</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="Y47" s="2"/>
       <c r="Z47" t="s" s="2">
-        <v>21</v>
+        <v>407</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>21</v>
@@ -8040,7 +8059,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -8055,27 +8074,27 @@
         <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>280</v>
+        <v>409</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>21</v>
+        <v>412</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8089,24 +8108,26 @@
         <v>80</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="N48" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="L48" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>21</v>
@@ -8155,7 +8176,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -8170,16 +8191,16 @@
         <v>101</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>21</v>
+        <v>280</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>21</v>
+        <v>411</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>21</v>
@@ -8187,10 +8208,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8213,13 +8234,13 @@
         <v>90</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>131</v>
+        <v>421</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8270,7 +8291,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -8285,13 +8306,13 @@
         <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>21</v>
+        <v>424</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>21</v>
@@ -8302,10 +8323,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8328,7 +8349,7 @@
         <v>90</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>426</v>
+        <v>131</v>
       </c>
       <c r="L50" t="s" s="2">
         <v>427</v>
@@ -8385,7 +8406,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -8400,13 +8421,13 @@
         <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>429</v>
+        <v>21</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>21</v>
@@ -8417,10 +8438,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8431,7 +8452,7 @@
         <v>79</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>21</v>
@@ -8443,18 +8464,16 @@
         <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>263</v>
+        <v>430</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="M51" t="s" s="2">
-        <v>433</v>
-      </c>
       <c r="N51" s="2"/>
-      <c r="O51" t="s" s="2">
-        <v>434</v>
-      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>21</v>
       </c>
@@ -8502,13 +8521,13 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>21</v>
@@ -8517,13 +8536,13 @@
         <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>21</v>
@@ -8534,10 +8553,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8557,21 +8576,21 @@
         <v>21</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>284</v>
+        <v>263</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="M52" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>21</v>
       </c>
@@ -8595,13 +8614,13 @@
         <v>21</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>209</v>
+        <v>21</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>441</v>
+        <v>21</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>442</v>
+        <v>21</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>21</v>
@@ -8619,7 +8638,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -8634,13 +8653,13 @@
         <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>21</v>
+        <v>439</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>21</v>
@@ -8651,10 +8670,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8665,7 +8684,7 @@
         <v>79</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>21</v>
@@ -8677,15 +8696,17 @@
         <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>445</v>
+        <v>284</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>443</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>444</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>21</v>
@@ -8710,13 +8731,13 @@
         <v>21</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>21</v>
+        <v>209</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>21</v>
+        <v>445</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>21</v>
+        <v>446</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>21</v>
@@ -8734,13 +8755,13 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>21</v>
@@ -8749,13 +8770,13 @@
         <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>448</v>
+        <v>21</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>21</v>
@@ -8766,10 +8787,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8792,13 +8813,13 @@
         <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="L54" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8849,7 +8870,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8864,13 +8885,13 @@
         <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>455</v>
+        <v>21</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>21</v>
@@ -8881,10 +8902,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8898,7 +8919,7 @@
         <v>80</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>21</v>
@@ -8907,17 +8928,15 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>461</v>
-      </c>
+        <v>457</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>21</v>
@@ -8966,7 +8985,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8981,13 +9000,13 @@
         <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>21</v>
+        <v>459</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>21</v>
@@ -8996,12 +9015,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9012,10 +9031,10 @@
         <v>79</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>21</v>
@@ -9024,15 +9043,17 @@
         <v>21</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>103</v>
+        <v>462</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>104</v>
+        <v>463</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>464</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>465</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>21</v>
@@ -9081,28 +9102,28 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>106</v>
+        <v>461</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>21</v>
+        <v>101</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>21</v>
+        <v>466</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>107</v>
+        <v>467</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>21</v>
@@ -9113,21 +9134,21 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>109</v>
+        <v>21</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>21</v>
@@ -9139,17 +9160,15 @@
         <v>21</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>21</v>
@@ -9186,31 +9205,31 @@
         <v>21</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>115</v>
+        <v>21</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>118</v>
+        <v>21</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>21</v>
@@ -9230,14 +9249,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>467</v>
+        <v>109</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9250,26 +9269,24 @@
         <v>21</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="K58" t="s" s="2">
         <v>110</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>468</v>
+        <v>111</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>469</v>
+        <v>112</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="O58" t="s" s="2">
-        <v>260</v>
-      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>21</v>
       </c>
@@ -9305,19 +9322,19 @@
         <v>21</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>470</v>
+        <v>117</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -9338,7 +9355,7 @@
         <v>21</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>241</v>
+        <v>107</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>21</v>
@@ -9349,43 +9366,45 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>21</v>
+        <v>471</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="J59" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="M59" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="N59" s="2"/>
+      <c r="N59" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="O59" t="s" s="2">
-        <v>475</v>
+        <v>260</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>21</v>
@@ -9434,19 +9453,19 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>21</v>
@@ -9455,21 +9474,21 @@
         <v>21</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>477</v>
+        <v>241</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>478</v>
+        <v>21</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9483,7 +9502,7 @@
         <v>89</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>21</v>
@@ -9492,17 +9511,17 @@
         <v>90</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>103</v>
+        <v>476</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>21</v>
@@ -9551,7 +9570,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9572,21 +9591,21 @@
         <v>21</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9597,10 +9616,10 @@
         <v>79</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>21</v>
@@ -9609,19 +9628,17 @@
         <v>90</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>284</v>
+        <v>103</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>21</v>
@@ -9646,13 +9663,13 @@
         <v>21</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>209</v>
+        <v>21</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>490</v>
+        <v>21</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>491</v>
+        <v>21</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>21</v>
@@ -9670,13 +9687,13 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>21</v>
@@ -9691,21 +9708,21 @@
         <v>21</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>493</v>
+        <v>488</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9716,7 +9733,7 @@
         <v>79</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>21</v>
@@ -9728,16 +9745,20 @@
         <v>90</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>103</v>
+        <v>284</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+        <v>491</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>493</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>21</v>
       </c>
@@ -9761,13 +9782,13 @@
         <v>21</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>21</v>
+        <v>209</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>21</v>
+        <v>494</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>21</v>
+        <v>495</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>21</v>
@@ -9785,13 +9806,13 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>21</v>
@@ -9806,13 +9827,13 @@
         <v>21</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="63" hidden="true">
@@ -9843,20 +9864,16 @@
         <v>90</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="M63" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>503</v>
-      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>21</v>
       </c>
@@ -9904,7 +9921,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9925,21 +9942,21 @@
         <v>21</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>505</v>
+        <v>481</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>21</v>
+        <v>497</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9953,7 +9970,7 @@
         <v>89</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>21</v>
@@ -9962,18 +9979,20 @@
         <v>90</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="O64" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="L64" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>21</v>
       </c>
@@ -9997,13 +10016,13 @@
         <v>21</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>209</v>
+        <v>21</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>511</v>
+        <v>21</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>512</v>
+        <v>21</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>21</v>
@@ -10021,7 +10040,7 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -10042,21 +10061,21 @@
         <v>21</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>515</v>
+        <v>21</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10079,20 +10098,18 @@
         <v>90</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>284</v>
+        <v>511</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>520</v>
-      </c>
+        <v>514</v>
+      </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>21</v>
       </c>
@@ -10119,10 +10136,10 @@
         <v>209</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>21</v>
@@ -10140,7 +10157,7 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -10161,21 +10178,21 @@
         <v>21</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>525</v>
+        <v>519</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10201,14 +10218,16 @@
         <v>284</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>522</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>523</v>
+      </c>
       <c r="O66" t="s" s="2">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>21</v>
@@ -10236,10 +10255,10 @@
         <v>209</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>21</v>
@@ -10257,7 +10276,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -10278,21 +10297,21 @@
         <v>21</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>534</v>
+        <v>529</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10318,16 +10337,14 @@
         <v>284</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>538</v>
-      </c>
+        <v>532</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>21</v>
@@ -10355,10 +10372,10 @@
         <v>209</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>21</v>
@@ -10376,7 +10393,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -10397,21 +10414,21 @@
         <v>21</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>544</v>
+        <v>538</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10422,7 +10439,7 @@
         <v>79</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>21</v>
@@ -10434,16 +10451,20 @@
         <v>90</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>546</v>
+        <v>284</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>547</v>
+        <v>540</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
+        <v>541</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>543</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>21</v>
       </c>
@@ -10467,13 +10488,13 @@
         <v>21</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>21</v>
+        <v>209</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>21</v>
+        <v>544</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>21</v>
+        <v>545</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>21</v>
@@ -10491,13 +10512,13 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>21</v>
@@ -10512,21 +10533,21 @@
         <v>21</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>21</v>
+        <v>547</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
-    <row r="69" hidden="true">
+    <row r="69">
       <c r="A69" t="s" s="2">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10537,25 +10558,25 @@
         <v>79</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>103</v>
+        <v>550</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>104</v>
+        <v>551</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>105</v>
+        <v>552</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10606,19 +10627,19 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>106</v>
+        <v>553</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>21</v>
+        <v>101</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>21</v>
@@ -10627,32 +10648,32 @@
         <v>21</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>21</v>
+        <v>554</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>109</v>
+        <v>21</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>21</v>
@@ -10664,17 +10685,15 @@
         <v>21</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>21</v>
@@ -10711,31 +10730,31 @@
         <v>21</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>115</v>
+        <v>21</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>118</v>
+        <v>21</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>21</v>
@@ -10755,21 +10774,21 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>21</v>
+        <v>109</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>21</v>
@@ -10778,21 +10797,21 @@
         <v>21</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>284</v>
+        <v>110</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>554</v>
+        <v>111</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="N71" s="2"/>
-      <c r="O71" t="s" s="2">
-        <v>556</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>21</v>
       </c>
@@ -10816,43 +10835,43 @@
         <v>21</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>209</v>
+        <v>21</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>557</v>
+        <v>21</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>558</v>
+        <v>21</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB71" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AC71" t="s" s="2">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="AD71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>559</v>
+        <v>117</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>21</v>
@@ -10861,21 +10880,21 @@
         <v>21</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>560</v>
+        <v>21</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10898,19 +10917,17 @@
         <v>90</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>562</v>
+        <v>284</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>565</v>
-      </c>
+        <v>559</v>
+      </c>
+      <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>21</v>
@@ -10935,13 +10952,13 @@
         <v>21</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>21</v>
+        <v>209</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>21</v>
+        <v>561</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>21</v>
+        <v>562</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>21</v>
@@ -10959,7 +10976,7 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10980,21 +10997,21 @@
         <v>21</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>543</v>
+        <v>21</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>568</v>
+        <v>564</v>
       </c>
     </row>
-    <row r="73" hidden="true">
+    <row r="73">
       <c r="A73" t="s" s="2">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11008,7 +11025,7 @@
         <v>89</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>21</v>
@@ -11017,19 +11034,19 @@
         <v>90</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="O73" t="s" s="2">
         <v>570</v>
-      </c>
-      <c r="L73" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>574</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>21</v>
@@ -11054,13 +11071,11 @@
         <v>21</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>21</v>
+        <v>571</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>21</v>
@@ -11078,7 +11093,7 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -11099,21 +11114,21 @@
         <v>21</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>576</v>
+        <v>547</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>577</v>
+        <v>573</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11136,19 +11151,19 @@
         <v>90</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="O74" t="s" s="2">
         <v>579</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>583</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>21</v>
@@ -11197,7 +11212,7 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -11218,21 +11233,21 @@
         <v>21</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>586</v>
+        <v>582</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11255,19 +11270,19 @@
         <v>90</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="O75" t="s" s="2">
         <v>588</v>
-      </c>
-      <c r="L75" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>592</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>21</v>
@@ -11316,7 +11331,7 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -11337,21 +11352,21 @@
         <v>21</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>21</v>
+        <v>591</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11374,17 +11389,19 @@
         <v>90</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="N76" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="O76" t="s" s="2">
         <v>597</v>
-      </c>
-      <c r="N76" s="2"/>
-      <c r="O76" t="s" s="2">
-        <v>598</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>21</v>
@@ -11433,7 +11450,7 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -11454,7 +11471,7 @@
         <v>21</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>21</v>
@@ -11488,19 +11505,21 @@
         <v>21</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="K77" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="L77" t="s" s="2">
         <v>601</v>
       </c>
-      <c r="L77" t="s" s="2">
+      <c r="M77" t="s" s="2">
         <v>602</v>
       </c>
-      <c r="M77" t="s" s="2">
+      <c r="N77" s="2"/>
+      <c r="O77" t="s" s="2">
         <v>603</v>
       </c>
-      <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>21</v>
       </c>
@@ -11548,7 +11567,7 @@
         <v>21</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -11566,24 +11585,24 @@
         <v>21</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>604</v>
+        <v>21</v>
       </c>
       <c r="AM77" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO77" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="2">
         <v>605</v>
       </c>
-      <c r="AN77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO77" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="78" hidden="true">
-      <c r="A78" t="s" s="2">
-        <v>606</v>
-      </c>
       <c r="B78" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11597,7 +11616,7 @@
         <v>89</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>21</v>
@@ -11606,13 +11625,13 @@
         <v>21</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>103</v>
+        <v>606</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>104</v>
+        <v>607</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>105</v>
+        <v>608</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11663,7 +11682,7 @@
         <v>21</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>106</v>
+        <v>605</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11675,16 +11694,16 @@
         <v>21</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>21</v>
+        <v>101</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>21</v>
+        <v>609</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>107</v>
+        <v>610</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>21</v>
@@ -11695,21 +11714,21 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>109</v>
+        <v>21</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>21</v>
@@ -11721,17 +11740,15 @@
         <v>21</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>21</v>
@@ -11780,19 +11797,19 @@
         <v>21</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>118</v>
+        <v>21</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>21</v>
@@ -11812,14 +11829,14 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>467</v>
+        <v>109</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -11832,26 +11849,24 @@
         <v>21</v>
       </c>
       <c r="I80" t="s" s="2">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="K80" t="s" s="2">
         <v>110</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>468</v>
+        <v>111</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>469</v>
+        <v>112</v>
       </c>
       <c r="N80" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="O80" t="s" s="2">
-        <v>260</v>
-      </c>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>21</v>
       </c>
@@ -11899,7 +11914,7 @@
         <v>21</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>470</v>
+        <v>117</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11920,7 +11935,7 @@
         <v>21</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>241</v>
+        <v>107</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>21</v>
@@ -11931,44 +11946,46 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>21</v>
+        <v>471</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I81" t="s" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>601</v>
+        <v>110</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>610</v>
+        <v>472</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>611</v>
+        <v>473</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="O81" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="O81" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="P81" t="s" s="2">
         <v>21</v>
       </c>
@@ -12016,19 +12033,19 @@
         <v>21</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>609</v>
+        <v>474</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>21</v>
@@ -12037,7 +12054,7 @@
         <v>21</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>613</v>
+        <v>241</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>21</v>
@@ -12074,15 +12091,17 @@
         <v>21</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>103</v>
+        <v>606</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>104</v>
+        <v>615</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N82" s="2"/>
+        <v>616</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>617</v>
+      </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>21</v>
@@ -12131,7 +12150,7 @@
         <v>21</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>106</v>
+        <v>614</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -12143,7 +12162,7 @@
         <v>21</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>21</v>
+        <v>101</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>21</v>
@@ -12152,7 +12171,7 @@
         <v>21</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>107</v>
+        <v>618</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>21</v>
@@ -12163,21 +12182,21 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>109</v>
+        <v>21</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>21</v>
@@ -12189,17 +12208,15 @@
         <v>21</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N83" s="2"/>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>21</v>
@@ -12248,19 +12265,19 @@
         <v>21</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>118</v>
+        <v>21</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>21</v>
@@ -12280,14 +12297,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>467</v>
+        <v>109</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -12300,26 +12317,24 @@
         <v>21</v>
       </c>
       <c r="I84" t="s" s="2">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="K84" t="s" s="2">
         <v>110</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>468</v>
+        <v>111</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>469</v>
+        <v>112</v>
       </c>
       <c r="N84" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="O84" t="s" s="2">
-        <v>260</v>
-      </c>
+      <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>21</v>
       </c>
@@ -12367,7 +12382,7 @@
         <v>21</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>470</v>
+        <v>117</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -12388,7 +12403,7 @@
         <v>21</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>241</v>
+        <v>107</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>21</v>
@@ -12399,42 +12414,46 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>21</v>
+        <v>471</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I85" t="s" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>588</v>
+        <v>110</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>618</v>
+        <v>472</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="N85" s="2"/>
-      <c r="O85" s="2"/>
+        <v>473</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="P85" t="s" s="2">
         <v>21</v>
       </c>
@@ -12482,19 +12501,19 @@
         <v>21</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>617</v>
+        <v>474</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>21</v>
@@ -12503,7 +12522,7 @@
         <v>21</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>620</v>
+        <v>241</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>21</v>
@@ -12514,10 +12533,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12540,7 +12559,7 @@
         <v>21</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>622</v>
+        <v>593</v>
       </c>
       <c r="L86" t="s" s="2">
         <v>623</v>
@@ -12597,7 +12616,7 @@
         <v>21</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -12655,13 +12674,13 @@
         <v>21</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12733,7 +12752,7 @@
         <v>21</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>21</v>
@@ -12744,10 +12763,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12770,20 +12789,16 @@
         <v>21</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="N88" t="s" s="2">
         <v>633</v>
       </c>
-      <c r="O88" t="s" s="2">
-        <v>634</v>
-      </c>
+      <c r="N88" s="2"/>
+      <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>21</v>
       </c>
@@ -12831,7 +12846,7 @@
         <v>21</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -12849,10 +12864,10 @@
         <v>21</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>635</v>
+        <v>21</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>21</v>
@@ -12863,10 +12878,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12889,18 +12904,20 @@
         <v>21</v>
       </c>
       <c r="K89" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="N89" t="s" s="2">
         <v>638</v>
       </c>
-      <c r="L89" t="s" s="2">
+      <c r="O89" t="s" s="2">
         <v>639</v>
       </c>
-      <c r="M89" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>21</v>
       </c>
@@ -12948,7 +12965,7 @@
         <v>21</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -12966,24 +12983,24 @@
         <v>21</v>
       </c>
       <c r="AL89" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="AN89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO89" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="2">
         <v>642</v>
       </c>
-      <c r="AM89" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="AN89" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO89" t="s" s="2">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="90" hidden="true">
-      <c r="A90" t="s" s="2">
-        <v>645</v>
-      </c>
       <c r="B90" t="s" s="2">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12997,7 +13014,7 @@
         <v>89</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>21</v>
@@ -13006,15 +13023,17 @@
         <v>21</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>588</v>
+        <v>643</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="N90" t="s" s="2">
         <v>646</v>
       </c>
-      <c r="M90" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="N90" s="2"/>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>21</v>
@@ -13063,7 +13082,7 @@
         <v>21</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -13081,24 +13100,24 @@
         <v>21</v>
       </c>
       <c r="AL90" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="AM90" t="s" s="2">
         <v>648</v>
       </c>
-      <c r="AM90" t="s" s="2">
+      <c r="AN90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO90" t="s" s="2">
         <v>649</v>
       </c>
-      <c r="AN90" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO90" t="s" s="2">
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="2">
         <v>650</v>
       </c>
-    </row>
-    <row r="91" hidden="true">
-      <c r="A91" t="s" s="2">
-        <v>651</v>
-      </c>
       <c r="B91" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13112,7 +13131,7 @@
         <v>89</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>21</v>
@@ -13121,17 +13140,15 @@
         <v>21</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>622</v>
+        <v>593</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>652</v>
       </c>
-      <c r="M91" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>654</v>
-      </c>
+      <c r="N91" s="2"/>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>21</v>
@@ -13180,7 +13197,7 @@
         <v>21</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -13198,24 +13215,24 @@
         <v>21</v>
       </c>
       <c r="AL91" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO91" t="s" s="2">
         <v>655</v>
-      </c>
-      <c r="AM91" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="AN91" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO91" t="s" s="2">
-        <v>21</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13238,15 +13255,17 @@
         <v>21</v>
       </c>
       <c r="K92" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>658</v>
       </c>
-      <c r="L92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>659</v>
       </c>
-      <c r="M92" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="N92" s="2"/>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>21</v>
@@ -13295,7 +13314,7 @@
         <v>21</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -13313,13 +13332,13 @@
         <v>21</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>21</v>
+        <v>660</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>661</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>398</v>
+        <v>21</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>21</v>
@@ -13353,13 +13372,13 @@
         <v>21</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>601</v>
+        <v>663</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13428,13 +13447,13 @@
         <v>21</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>665</v>
+        <v>21</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>666</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>21</v>
+        <v>402</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>21</v>
@@ -13468,13 +13487,13 @@
         <v>21</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>103</v>
+        <v>606</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>104</v>
+        <v>668</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>105</v>
+        <v>669</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13525,7 +13544,7 @@
         <v>21</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>106</v>
+        <v>667</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -13537,16 +13556,16 @@
         <v>21</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>21</v>
+        <v>101</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>21</v>
+        <v>670</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>107</v>
+        <v>671</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>21</v>
@@ -13557,21 +13576,21 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>109</v>
+        <v>21</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>21</v>
@@ -13583,17 +13602,15 @@
         <v>21</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N95" s="2"/>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>21</v>
@@ -13642,19 +13659,19 @@
         <v>21</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>118</v>
+        <v>21</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>21</v>
@@ -13674,14 +13691,14 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>467</v>
+        <v>109</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -13694,26 +13711,24 @@
         <v>21</v>
       </c>
       <c r="I96" t="s" s="2">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="K96" t="s" s="2">
         <v>110</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>468</v>
+        <v>111</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>469</v>
+        <v>112</v>
       </c>
       <c r="N96" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="O96" t="s" s="2">
-        <v>260</v>
-      </c>
+      <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>21</v>
       </c>
@@ -13761,7 +13776,7 @@
         <v>21</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>470</v>
+        <v>117</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -13782,7 +13797,7 @@
         <v>21</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>241</v>
+        <v>107</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>21</v>
@@ -13793,44 +13808,46 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>21</v>
+        <v>471</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I97" t="s" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>507</v>
+        <v>110</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>671</v>
+        <v>472</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>672</v>
+        <v>473</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>673</v>
-      </c>
-      <c r="O97" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="O97" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="P97" t="s" s="2">
         <v>21</v>
       </c>
@@ -13854,13 +13871,13 @@
         <v>21</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>209</v>
+        <v>21</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>674</v>
+        <v>21</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>675</v>
+        <v>21</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>21</v>
@@ -13878,42 +13895,42 @@
         <v>21</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>670</v>
+        <v>474</v>
       </c>
       <c r="AG97" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>665</v>
+        <v>21</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>676</v>
+        <v>241</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>677</v>
+        <v>21</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13921,7 +13938,7 @@
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G98" t="s" s="2">
         <v>89</v>
@@ -13936,15 +13953,17 @@
         <v>21</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>284</v>
+        <v>511</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>680</v>
-      </c>
-      <c r="N98" s="2"/>
+        <v>677</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>678</v>
+      </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>21</v>
@@ -13972,10 +13991,10 @@
         <v>209</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>21</v>
@@ -13993,10 +14012,10 @@
         <v>21</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="AG98" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH98" t="s" s="2">
         <v>89</v>
@@ -14011,24 +14030,24 @@
         <v>21</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>683</v>
+        <v>670</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>685</v>
+        <v>682</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14051,13 +14070,13 @@
         <v>21</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>687</v>
+        <v>284</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -14084,13 +14103,13 @@
         <v>21</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>21</v>
+        <v>209</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>21</v>
+        <v>686</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>21</v>
+        <v>687</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>21</v>
@@ -14108,7 +14127,7 @@
         <v>21</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -14123,38 +14142,38 @@
         <v>101</v>
       </c>
       <c r="AK99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO99" t="s" s="2">
         <v>690</v>
-      </c>
-      <c r="AL99" t="s" s="2">
-        <v>683</v>
-      </c>
-      <c r="AM99" t="s" s="2">
-        <v>691</v>
-      </c>
-      <c r="AN99" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO99" t="s" s="2">
-        <v>21</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>693</v>
+        <v>21</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>21</v>
@@ -14166,17 +14185,15 @@
         <v>21</v>
       </c>
       <c r="K100" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>694</v>
       </c>
-      <c r="L100" t="s" s="2">
-        <v>695</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>696</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>697</v>
-      </c>
+      <c r="N100" s="2"/>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>21</v>
@@ -14225,13 +14242,13 @@
         <v>21</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>21</v>
@@ -14240,13 +14257,13 @@
         <v>101</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>21</v>
+        <v>695</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>21</v>
+        <v>688</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>21</v>
@@ -14257,14 +14274,14 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>21</v>
+        <v>698</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -14283,16 +14300,16 @@
         <v>21</v>
       </c>
       <c r="K101" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="L101" t="s" s="2">
         <v>700</v>
       </c>
-      <c r="L101" t="s" s="2">
+      <c r="M101" t="s" s="2">
         <v>701</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="N101" t="s" s="2">
         <v>702</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>703</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14342,7 +14359,7 @@
         <v>21</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -14357,33 +14374,150 @@
         <v>101</v>
       </c>
       <c r="AK101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="AN101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO101" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="102" hidden="true">
+      <c r="A102" t="s" s="2">
         <v>704</v>
       </c>
-      <c r="AL101" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM101" t="s" s="2">
+      <c r="B102" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E102" s="2"/>
+      <c r="F102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K102" t="s" s="2">
         <v>705</v>
       </c>
-      <c r="AN101" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO101" t="s" s="2">
+      <c r="L102" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="O102" s="2"/>
+      <c r="P102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q102" s="2"/>
+      <c r="R102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF102" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="AG102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ102" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK102" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="AN102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO102" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO101">
-    <filterColumn colId="6">
+  <autoFilter ref="A1:AO102">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI100">
+  <conditionalFormatting sqref="A2:AI101">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/publication/web-root/cibmtr-reporting/StructureDefinition-cibmtr-medication-request.xlsx
+++ b/publication/web-root/cibmtr-reporting/StructureDefinition-cibmtr-medication-request.xlsx
@@ -60,19 +60,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T07:35:08-05:00</t>
+    <t>2026-06-25T19:24:07-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the National Marrow Donor Program</t>
+    <t>The Medical College of Wisconsin, Inc. and NMDP</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the National Marrow Donor Program (http://www.cibmtr.org)</t>
+    <t>The Medical College of Wisconsin, Inc. and NMDP (http://www.cibmtr.org)</t>
   </si>
   <si>
     <t>Bob Milius (bmilius@nmdp.org)</t>

--- a/publication/web-root/cibmtr-reporting/StructureDefinition-cibmtr-medication-request.xlsx
+++ b/publication/web-root/cibmtr-reporting/StructureDefinition-cibmtr-medication-request.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$102</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3761" uniqueCount="706">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3797" uniqueCount="711">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.10</t>
+    <t>0.1.12</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,19 +60,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T10:10:52-05:00</t>
+    <t>2026-08-27T20:49:22-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the National Marrow Donor Program</t>
+    <t>The Medical College of Wisconsin, Inc. and NMDP</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the National Marrow Donor Program (http://www.cibmtr.org)</t>
+    <t>The Medical College of Wisconsin, Inc. and NMDP (http://www.cibmtr.org)</t>
   </si>
   <si>
     <t>Bob Milius (bmilius@nmdp.org)</t>
@@ -269,11 +269,13 @@
     <t>Ordering of medication for patient or group</t>
   </si>
   <si>
-    <t>The US Core Medication Request (Order) Profile is based upon the core FHIR MedicationRequest Resource and created to meet the 2015 Edition Common Clinical Data Set 'Medications' requirements.</t>
+    <t>\-</t>
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}mcode-reason-required:One of reasonCode or reasonReference SHALL be present {reasonCode.exists() or reasonReference.exists()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}us-core-21:requester SHALL be present if intent is "order" {(intent='order' or intent='original-order' or intent='reflex-order'or intent='filler-order' or intent='instance-order') implies requester.exists()}mcode-reason-required:One of reasonCode or reasonReference SHALL be present {reasonCode.exists() or reasonReference.exists()}termination-reason-code-invariant:When status is stopped, only certain statusReason values are allowed {status = 'stopped' and statusReason.exists() and statusReason.coding.exists() implies statusReason.coding.exists(system = 'http://snomed.info/sct' and (code = '182992009' or code = '266721009' or code = '407563006' or code = '160932005' or code = '105480006' or code = '184081006' or code = '309846006' or code = '399307001' or code = '419620001' or code = '7058009' or code = '443729008' or code = '77386006'))}termination-reason-invariant:Certain statusReason values are allowed only when status is stopped {statusReason.exists() and statusReason.coding.exists(
+      system = 'http://snomed.info/sct' and (code = '182992009' or code = '266721009' or code = '407563006' or code = '160932005' or
+ code = '105480006' or code = '184081006' or code = '309846006' or code = '399307001' or  code = '419620001' or code = '7058009' or code = '443729008' or code = '77386006')) implies status = 'stopped'}</t>
   </si>
   <si>
     <t>Request</t>
@@ -800,20 +802,20 @@
 </t>
   </si>
   <si>
-    <t>MedicationRequest.extension:terminationReason</t>
-  </si>
-  <si>
-    <t>terminationReason</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://hl7.org/fhir/us/mcode/StructureDefinition/mcode-treatment-termination-reason}
+    <t>MedicationRequest.extension:normalizationBasis</t>
+  </si>
+  <si>
+    <t>normalizationBasis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/us/mcode/StructureDefinition/mcode-normalization-basis}
 </t>
   </si>
   <si>
-    <t>Treatment Termination Reason Extension</t>
-  </si>
-  <si>
-    <t>A code explaining the unplanned or premature termination, or normal completion, of a plan of treatment, course of medication, or research study.</t>
+    <t>Normalization Basis Extension</t>
+  </si>
+  <si>
+    <t>The method (e.g., body weight, body surface area, flat dose, age) used to normalize the medication dosage.</t>
   </si>
   <si>
     <t>MedicationRequest.modifierExtension</t>
@@ -866,7 +868,7 @@
     <t>MedicationRequest.status</t>
   </si>
   <si>
-    <t>active | on-hold | cancelled | completed | entered-in-error | stopped | draft | unknown</t>
+    <t>(USCDI) active | on-hold | cancelled | completed | entered-in-error | stopped | draft | unknown</t>
   </si>
   <si>
     <t>A code specifying the current state of the order.  Generally, this will be active or completed state.</t>
@@ -912,10 +914,7 @@
     <t>This is generally only used for "exception" statuses such as "suspended" or "cancelled". The reason why the MedicationRequest was created at all is captured in reasonCode, not here.</t>
   </si>
   <si>
-    <t>Identifies the reasons for a given status.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationrequest-status-reason</t>
+    <t>http://hl7.org/fhir/us/mcode/ValueSet/mcode-treatment-termination-reason-vs</t>
   </si>
   <si>
     <t>Request.statusReason</t>
@@ -927,7 +926,7 @@
     <t>MedicationRequest.intent</t>
   </si>
   <si>
-    <t>proposal | plan | order | original-order | reflex-order | filler-order | instance-order | option</t>
+    <t>(USCDI) proposal | plan | order | original-order | reflex-order | filler-order | instance-order | option</t>
   </si>
   <si>
     <t>Whether the request is a proposal, plan, or an original order.</t>
@@ -946,6 +945,10 @@
     <t>http://hl7.org/fhir/ValueSet/medicationrequest-intent</t>
   </si>
   <si>
+    <t xml:space="preserve">us-core-21
+</t>
+  </si>
+  <si>
     <t>Request.intent</t>
   </si>
   <si>
@@ -958,7 +961,7 @@
     <t>MedicationRequest.category</t>
   </si>
   <si>
-    <t>Type of medication usage</t>
+    <t>(USCDI) Type of medication usage</t>
   </si>
   <si>
     <t>Indicates the type of medication request (for example, where the medication is expected to be consumed or administered (i.e. inpatient or outpatient)).</t>
@@ -967,10 +970,14 @@
     <t>The category can be used to include where the medication is expected to be consumed or other types of requests.</t>
   </si>
   <si>
-    <t>The type of medication order.</t>
+    <t>A coded concept identifying the category of medication request.  For example, where the medication is to be consumed or administered, or the type of medication treatment.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/medicationrequest-category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
   </si>
   <si>
     <t>Message/Body/NewRx/MedicationPrescribed/Directions@@ -983,6 +990,15 @@
     <t>.inboundRelationship[typeCode=COMP].source[classCode=OBS, moodCode=EVN, code="type of medication usage"].value</t>
   </si>
   <si>
+    <t>MedicationRequest.category:us-core</t>
+  </si>
+  <si>
+    <t>us-core</t>
+  </si>
+  <si>
+    <t>The type of medication order. Note that other codes are permitted, see [Required Bindings When Slicing by Value Sets](http://hl7.org/fhir/us/core/general-requirements.html#required-bindings-when-slicing-by-valuesets)</t>
+  </si>
+  <si>
     <t>MedicationRequest.priority</t>
   </si>
   <si>
@@ -1026,10 +1042,10 @@
   </si>
   <si>
     <t>boolean
-Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitioner|http://hl7.org/fhir/us/core/StructureDefinition/us-core-organization|http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient|http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitionerrole|RelatedPerson)</t>
-  </si>
-  <si>
-    <t>Reported rather than primary record</t>
+Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitioner|http://hl7.org/fhir/us/core/StructureDefinition/us-core-organization|http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient|http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitionerrole|http://hl7.org/fhir/us/core/StructureDefinition/us-core-relatedperson)</t>
+  </si>
+  <si>
+    <t>(USCDI) Reported rather than primary record</t>
   </si>
   <si>
     <t>Indicates if this record was captured as a secondary 'reported' record rather than as an original primary source-of-truth record.  It may also indicate the source of the report.</t>
@@ -1045,7 +1061,7 @@
 Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-medication)</t>
   </si>
   <si>
-    <t>Medication to be taken</t>
+    <t>(USCDI) Medication to be taken</t>
   </si>
   <si>
     <t>Identifies the medication being requested. This is a link to a resource that represents the medication which may be the details of the medication or simply an attribute carrying a code that identifies the medication from a known list of medications.</t>
@@ -1085,7 +1101,7 @@
 </t>
   </si>
   <si>
-    <t>Who or group medication request is for</t>
+    <t>(USCDI) Who or group medication request is for</t>
   </si>
   <si>
     <t>The patient receiving the medication.</t>
@@ -1118,7 +1134,7 @@
 </t>
   </si>
   <si>
-    <t>Encounter created as part of encounter/admission/stay</t>
+    <t>(USCDI) Encounter created as part of encounter/admission/stay</t>
   </si>
   <si>
     <t>The Encounter during which this [x] was created or to which the creation of this record is tightly associated.</t>
@@ -1165,7 +1181,7 @@
 </t>
   </si>
   <si>
-    <t>When request was initially authored</t>
+    <t>(USCDI) When request was initially authored</t>
   </si>
   <si>
     <t>The date (and perhaps time) when the prescription was initially written or authored on.</t>
@@ -1193,7 +1209,7 @@
 </t>
   </si>
   <si>
-    <t>Who/What requested the Request</t>
+    <t>(USCDI) Who/What requested the Request</t>
   </si>
   <si>
     <t>The individual, organization, or device that initiated the request and has responsibility for its activation.</t>
@@ -1273,7 +1289,7 @@
     <t>MedicationRequest.reasonCode</t>
   </si>
   <si>
-    <t>Reason or indication for ordering or not ordering the medication</t>
+    <t>(USCDI) Reason or indication for ordering or not ordering the medication</t>
   </si>
   <si>
     <t>The reason or the indication for ordering or not ordering the medication.</t>
@@ -1303,11 +1319,11 @@
     <t>MedicationRequest.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/mcode/StructureDefinition/mcode-primary-cancer-condition|http://hl7.org/fhir/us/mcode/StructureDefinition/mcode-secondary-cancer-condition)
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-condition-problems-health-concerns)
 </t>
   </si>
   <si>
-    <t>Condition or observation that supports why the prescription is being written</t>
+    <t>(USCDI) US Core Condition or Observation that supports the prescription</t>
   </si>
   <si>
     <t>Condition or observation that supports why the medication was ordered.</t>
@@ -1456,7 +1472,7 @@
 </t>
   </si>
   <si>
-    <t>How the medication should be taken</t>
+    <t>(USCDI) How the medication should be taken</t>
   </si>
   <si>
     <t>Indicates how the medication is to be used by the patient.</t>
@@ -1522,7 +1538,7 @@
     <t>MedicationRequest.dosageInstruction.text</t>
   </si>
   <si>
-    <t>Free text dosage instructions e.g. SIG</t>
+    <t>(USCDI) Free text dosage instructions e.g. SIG</t>
   </si>
   <si>
     <t>Free text dosage instructions e.g. SIG.</t>
@@ -1583,7 +1599,7 @@
 </t>
   </si>
   <si>
-    <t>When medication should be administered</t>
+    <t>(USCDI) When medication should be administered</t>
   </si>
   <si>
     <t>When medication should be administered.</t>
@@ -1726,7 +1742,7 @@
 </t>
   </si>
   <si>
-    <t>Amount of medication administered</t>
+    <t>(USCDI) Amount of medication administered</t>
   </si>
   <si>
     <t>The amount of medication administered.</t>
@@ -1771,11 +1787,11 @@
     <t>MedicationRequest.dosageInstruction.doseAndRate.dose[x]</t>
   </si>
   <si>
-    <t>Range
-Quantity {SimpleQuantity}</t>
-  </si>
-  <si>
-    <t>Amount of medication per dose</t>
+    <t>Quantity
+Range</t>
+  </si>
+  <si>
+    <t>(USCDI) Amount of medication per dose</t>
   </si>
   <si>
     <t>Amount of medication per dose.</t>
@@ -1785,6 +1801,9 @@
   </si>
   <si>
     <t>The amount of therapeutic or other substance given at one administration event.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/ucum-common</t>
   </si>
   <si>
     <t>Dosage.doseAndRate.dose[x]</t>
@@ -1898,7 +1917,7 @@
 </t>
   </si>
   <si>
-    <t>Medication supply authorization</t>
+    <t>(USCDI) Medication supply authorization</t>
   </si>
   <si>
     <t>Indicates the specific details for the dispense or medication supply part of a medication request (also known as a Medication Prescription or Medication Order).  Note that this information is not always sent with the order.  There may be in some settings (e.g. hospitals) institutional or system support for completing the dispense details in the pharmacy department.</t>
@@ -2012,7 +2031,7 @@
 </t>
   </si>
   <si>
-    <t>Number of refills authorized</t>
+    <t>(USCDI) Number of refills authorized</t>
   </si>
   <si>
     <t>An integer indicating the number of times, in addition to the original dispense, (aka refills or repeats) that the patient can receive the prescribed medication. Usage Notes: This integer does not include the original order dispense. This means that if an order indicates dispense 30 tablets plus "3 repeats", then the order can be dispensed a total of 4 times and the patient can receive a total of 120 tablets.  A prescriber may explicitly say that zero refills are permitted after the initial dispense.</t>
@@ -2033,7 +2052,7 @@
     <t>MedicationRequest.dispenseRequest.quantity</t>
   </si>
   <si>
-    <t>Amount of medication to supply per dispense</t>
+    <t>(USCDI) Amount of medication to supply per dispense</t>
   </si>
   <si>
     <t>The amount that is to be dispensed for one fill.</t>
@@ -2540,12 +2559,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO101"/>
+  <dimension ref="A1:AO102"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="54.0390625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="54.0390625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="16.30859375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="16.05078125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.8125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.21484375" customWidth="true" bestFit="true"/>
@@ -2553,7 +2572,7 @@
     <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="243.55859375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2567,8 +2586,8 @@
     <col min="22" max="22" width="14.4296875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="172.55078125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="63.33203125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="177.9765625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="65.70703125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="35.90625" customWidth="true" bestFit="true"/>
@@ -2746,7 +2765,9 @@
       <c r="M2" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="N2" s="2"/>
+      <c r="N2" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
         <v>21</v>
@@ -5629,7 +5650,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
         <v>252</v>
       </c>
@@ -5647,10 +5668,10 @@
         <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>21</v>
@@ -6099,7 +6120,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
         <v>283</v>
       </c>
@@ -6118,7 +6139,7 @@
         <v>89</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>21</v>
@@ -6162,13 +6183,11 @@
         <v>21</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="Y31" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="Y31" s="2"/>
+      <c r="Z31" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="Z31" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>21</v>
@@ -6201,13 +6220,13 @@
         <v>101</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM31" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="AL31" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>291</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>21</v>
@@ -6218,10 +6237,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6247,13 +6266,13 @@
         <v>179</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6282,11 +6301,11 @@
         <v>276</v>
       </c>
       <c r="Y32" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="Z32" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="Z32" t="s" s="2">
-        <v>297</v>
-      </c>
       <c r="AA32" t="s" s="2">
         <v>21</v>
       </c>
@@ -6303,7 +6322,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>89</v>
@@ -6312,7 +6331,7 @@
         <v>89</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>21</v>
+        <v>297</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>101</v>
@@ -6333,7 +6352,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
         <v>301</v>
       </c>
@@ -6396,7 +6415,7 @@
         <v>21</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="Y33" t="s" s="2">
         <v>305</v>
@@ -6408,16 +6427,14 @@
         <v>21</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>307</v>
+      </c>
+      <c r="AC33" s="2"/>
       <c r="AD33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="AF33" t="s" s="2">
         <v>301</v>
@@ -6438,10 +6455,10 @@
         <v>21</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>300</v>
@@ -6450,14 +6467,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="C34" s="2"/>
+        <v>301</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>311</v>
+      </c>
       <c r="D34" t="s" s="2">
         <v>21</v>
       </c>
@@ -6466,27 +6485,29 @@
         <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>179</v>
+        <v>284</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>21</v>
@@ -6517,7 +6538,7 @@
         <v>312</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>21</v>
@@ -6535,13 +6556,13 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>21</v>
@@ -6550,16 +6571,16 @@
         <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>314</v>
+        <v>21</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>21</v>
+        <v>308</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>316</v>
+        <v>300</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>21</v>
@@ -6567,10 +6588,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6587,23 +6608,21 @@
         <v>21</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="J35" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>320</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>21</v>
@@ -6628,13 +6647,13 @@
         <v>21</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>21</v>
+        <v>276</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>21</v>
+        <v>316</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>21</v>
+        <v>317</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>21</v>
@@ -6652,7 +6671,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6667,27 +6686,27 @@
         <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>21</v>
+        <v>318</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM35" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AN35" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AO35" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="36" hidden="true">
+      <c r="A36" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="AN35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s" s="2">
-        <v>322</v>
-      </c>
       <c r="B36" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6701,24 +6720,26 @@
         <v>89</v>
       </c>
       <c r="H36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I36" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="I36" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="J36" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="M36" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>21</v>
@@ -6767,7 +6788,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6788,7 +6809,7 @@
         <v>21</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>21</v>
@@ -6799,10 +6820,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6810,7 +6831,7 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>89</v>
@@ -6825,17 +6846,15 @@
         <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="M37" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>331</v>
-      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>21</v>
@@ -6860,11 +6879,13 @@
         <v>21</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="Y37" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z37" t="s" s="2">
-        <v>332</v>
+        <v>21</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>21</v>
@@ -6882,10 +6903,10 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH37" t="s" s="2">
         <v>89</v>
@@ -6897,27 +6918,27 @@
         <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>333</v>
+        <v>21</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>334</v>
+        <v>21</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>336</v>
+        <v>21</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>337</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6940,16 +6961,16 @@
         <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6975,13 +6996,11 @@
         <v>21</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y38" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>21</v>
+        <v>336</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>21</v>
@@ -6999,7 +7018,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>89</v>
@@ -7014,27 +7033,27 @@
         <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7042,7 +7061,7 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>89</v>
@@ -7054,19 +7073,19 @@
         <v>21</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7116,10 +7135,10 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>89</v>
@@ -7131,27 +7150,27 @@
         <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>280</v>
+        <v>348</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>356</v>
+        <v>351</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7162,10 +7181,10 @@
         <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>21</v>
@@ -7174,15 +7193,17 @@
         <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>355</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>356</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>21</v>
@@ -7231,13 +7252,13 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>21</v>
@@ -7246,27 +7267,27 @@
         <v>101</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AN40" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="AO40" t="s" s="2">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="41" hidden="true">
+      <c r="A41" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="AL40" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="AO40" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s" s="2">
-        <v>363</v>
-      </c>
       <c r="B41" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7277,25 +7298,25 @@
         <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="L41" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7346,13 +7367,13 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>21</v>
@@ -7361,27 +7382,27 @@
         <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>368</v>
+        <v>21</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>370</v>
+        <v>359</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>371</v>
+        <v>21</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7404,13 +7425,13 @@
         <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7461,7 +7482,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -7476,27 +7497,27 @@
         <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AO42" t="s" s="2">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="AL42" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="43" hidden="true">
-      <c r="A43" t="s" s="2">
-        <v>378</v>
-      </c>
       <c r="B43" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7510,22 +7531,22 @@
         <v>89</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="L43" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7576,7 +7597,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -7585,22 +7606,22 @@
         <v>89</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>21</v>
+        <v>297</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>383</v>
+        <v>349</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>21</v>
@@ -7608,10 +7629,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7631,20 +7652,18 @@
         <v>21</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>284</v>
+        <v>383</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>388</v>
-      </c>
+        <v>385</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>21</v>
@@ -7669,13 +7688,13 @@
         <v>21</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>209</v>
+        <v>21</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>389</v>
+        <v>21</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>390</v>
+        <v>21</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>21</v>
@@ -7693,7 +7712,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7708,16 +7727,16 @@
         <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>21</v>
+        <v>388</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>21</v>
@@ -7725,10 +7744,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7748,18 +7767,20 @@
         <v>21</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>394</v>
+        <v>284</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>391</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>392</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>21</v>
@@ -7784,13 +7805,13 @@
         <v>21</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>21</v>
+        <v>209</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>21</v>
+        <v>393</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>21</v>
+        <v>394</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>21</v>
@@ -7808,7 +7829,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7823,27 +7844,27 @@
         <v>101</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>21</v>
+        <v>395</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM45" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AN45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO45" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="46" hidden="true">
+      <c r="A46" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="AN45" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="AO45" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s" s="2">
-        <v>399</v>
-      </c>
       <c r="B46" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7854,10 +7875,10 @@
         <v>79</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>21</v>
@@ -7866,17 +7887,15 @@
         <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>284</v>
+        <v>398</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="M46" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>402</v>
-      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>21</v>
@@ -7901,11 +7920,13 @@
         <v>21</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="Y46" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z46" t="s" s="2">
-        <v>403</v>
+        <v>21</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>21</v>
@@ -7923,13 +7944,13 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>21</v>
@@ -7938,27 +7959,27 @@
         <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>404</v>
+        <v>21</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>405</v>
+        <v>21</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>408</v>
+        <v>21</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7981,16 +8002,16 @@
         <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>410</v>
+        <v>284</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8016,13 +8037,11 @@
         <v>21</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="Y47" s="2"/>
       <c r="Z47" t="s" s="2">
-        <v>21</v>
+        <v>407</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>21</v>
@@ -8040,7 +8059,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -8055,27 +8074,27 @@
         <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>280</v>
+        <v>409</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>21</v>
+        <v>412</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8089,24 +8108,26 @@
         <v>80</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="N48" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="L48" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>21</v>
@@ -8155,7 +8176,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -8170,16 +8191,16 @@
         <v>101</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>21</v>
+        <v>280</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>21</v>
+        <v>411</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>21</v>
@@ -8187,10 +8208,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8213,13 +8234,13 @@
         <v>90</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>131</v>
+        <v>421</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8270,7 +8291,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -8285,13 +8306,13 @@
         <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>21</v>
+        <v>424</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>21</v>
@@ -8302,10 +8323,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8328,7 +8349,7 @@
         <v>90</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>426</v>
+        <v>131</v>
       </c>
       <c r="L50" t="s" s="2">
         <v>427</v>
@@ -8385,7 +8406,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -8400,13 +8421,13 @@
         <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>429</v>
+        <v>21</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>21</v>
@@ -8417,10 +8438,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8431,7 +8452,7 @@
         <v>79</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>21</v>
@@ -8443,18 +8464,16 @@
         <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>263</v>
+        <v>430</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="M51" t="s" s="2">
-        <v>433</v>
-      </c>
       <c r="N51" s="2"/>
-      <c r="O51" t="s" s="2">
-        <v>434</v>
-      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>21</v>
       </c>
@@ -8502,13 +8521,13 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>21</v>
@@ -8517,13 +8536,13 @@
         <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>21</v>
@@ -8534,10 +8553,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8557,21 +8576,21 @@
         <v>21</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>284</v>
+        <v>263</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="M52" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>21</v>
       </c>
@@ -8595,13 +8614,13 @@
         <v>21</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>209</v>
+        <v>21</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>441</v>
+        <v>21</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>442</v>
+        <v>21</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>21</v>
@@ -8619,7 +8638,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -8634,13 +8653,13 @@
         <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>21</v>
+        <v>439</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>21</v>
@@ -8651,10 +8670,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8665,7 +8684,7 @@
         <v>79</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>21</v>
@@ -8677,15 +8696,17 @@
         <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>445</v>
+        <v>284</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>443</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>444</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>21</v>
@@ -8710,13 +8731,13 @@
         <v>21</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>21</v>
+        <v>209</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>21</v>
+        <v>445</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>21</v>
+        <v>446</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>21</v>
@@ -8734,13 +8755,13 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>21</v>
@@ -8749,13 +8770,13 @@
         <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>448</v>
+        <v>21</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>21</v>
@@ -8766,10 +8787,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8792,13 +8813,13 @@
         <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="L54" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8849,7 +8870,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8864,27 +8885,27 @@
         <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO54" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="55" hidden="true">
+      <c r="A55" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="AL54" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s" s="2">
-        <v>457</v>
-      </c>
       <c r="B55" t="s" s="2">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8898,7 +8919,7 @@
         <v>80</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>21</v>
@@ -8907,17 +8928,15 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>461</v>
-      </c>
+        <v>457</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>21</v>
@@ -8966,7 +8985,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8981,13 +9000,13 @@
         <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>21</v>
+        <v>459</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>21</v>
@@ -8996,12 +9015,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9012,10 +9031,10 @@
         <v>79</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>21</v>
@@ -9024,15 +9043,17 @@
         <v>21</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>103</v>
+        <v>462</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>104</v>
+        <v>463</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>464</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>465</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>21</v>
@@ -9081,28 +9102,28 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>106</v>
+        <v>461</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>21</v>
+        <v>101</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>21</v>
+        <v>466</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>107</v>
+        <v>467</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>21</v>
@@ -9113,21 +9134,21 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>109</v>
+        <v>21</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>21</v>
@@ -9139,17 +9160,15 @@
         <v>21</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>21</v>
@@ -9186,31 +9205,31 @@
         <v>21</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>115</v>
+        <v>21</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>118</v>
+        <v>21</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>21</v>
@@ -9230,14 +9249,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>467</v>
+        <v>109</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9250,26 +9269,24 @@
         <v>21</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="K58" t="s" s="2">
         <v>110</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>468</v>
+        <v>111</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>469</v>
+        <v>112</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="O58" t="s" s="2">
-        <v>260</v>
-      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>21</v>
       </c>
@@ -9305,19 +9322,19 @@
         <v>21</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>470</v>
+        <v>117</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -9338,7 +9355,7 @@
         <v>21</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>241</v>
+        <v>107</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>21</v>
@@ -9349,43 +9366,45 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>21</v>
+        <v>471</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="J59" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="M59" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="N59" s="2"/>
+      <c r="N59" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="O59" t="s" s="2">
-        <v>475</v>
+        <v>260</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>21</v>
@@ -9434,19 +9453,19 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>21</v>
@@ -9455,21 +9474,21 @@
         <v>21</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>477</v>
+        <v>241</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>478</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9483,7 +9502,7 @@
         <v>89</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>21</v>
@@ -9492,17 +9511,17 @@
         <v>90</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>103</v>
+        <v>476</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>21</v>
@@ -9551,7 +9570,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9572,21 +9591,21 @@
         <v>21</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9597,10 +9616,10 @@
         <v>79</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>21</v>
@@ -9609,19 +9628,17 @@
         <v>90</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>284</v>
+        <v>103</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>21</v>
@@ -9646,13 +9663,13 @@
         <v>21</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>209</v>
+        <v>21</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>490</v>
+        <v>21</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>491</v>
+        <v>21</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>21</v>
@@ -9670,13 +9687,13 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>21</v>
@@ -9691,21 +9708,21 @@
         <v>21</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>493</v>
+        <v>488</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9716,7 +9733,7 @@
         <v>79</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>21</v>
@@ -9728,16 +9745,20 @@
         <v>90</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>103</v>
+        <v>284</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+        <v>491</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>493</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>21</v>
       </c>
@@ -9761,13 +9782,13 @@
         <v>21</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>21</v>
+        <v>209</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>21</v>
+        <v>494</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>21</v>
+        <v>495</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>21</v>
@@ -9785,13 +9806,13 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>21</v>
@@ -9806,13 +9827,13 @@
         <v>21</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="63" hidden="true">
@@ -9843,20 +9864,16 @@
         <v>90</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="M63" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>503</v>
-      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>21</v>
       </c>
@@ -9904,7 +9921,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9925,21 +9942,21 @@
         <v>21</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>505</v>
+        <v>481</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>21</v>
+        <v>497</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9953,7 +9970,7 @@
         <v>89</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>21</v>
@@ -9962,18 +9979,20 @@
         <v>90</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="O64" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="L64" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>21</v>
       </c>
@@ -9997,13 +10016,13 @@
         <v>21</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>209</v>
+        <v>21</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>511</v>
+        <v>21</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>512</v>
+        <v>21</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>21</v>
@@ -10021,7 +10040,7 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -10042,21 +10061,21 @@
         <v>21</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>515</v>
+        <v>21</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10079,20 +10098,18 @@
         <v>90</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>284</v>
+        <v>511</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>520</v>
-      </c>
+        <v>514</v>
+      </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>21</v>
       </c>
@@ -10119,10 +10136,10 @@
         <v>209</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>21</v>
@@ -10140,7 +10157,7 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -10161,21 +10178,21 @@
         <v>21</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>525</v>
+        <v>519</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10201,14 +10218,16 @@
         <v>284</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>522</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>523</v>
+      </c>
       <c r="O66" t="s" s="2">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>21</v>
@@ -10236,10 +10255,10 @@
         <v>209</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>21</v>
@@ -10257,7 +10276,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -10278,21 +10297,21 @@
         <v>21</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>534</v>
+        <v>529</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10318,16 +10337,14 @@
         <v>284</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>538</v>
-      </c>
+        <v>532</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>21</v>
@@ -10355,10 +10372,10 @@
         <v>209</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>21</v>
@@ -10376,7 +10393,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -10397,21 +10414,21 @@
         <v>21</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>544</v>
+        <v>538</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10422,7 +10439,7 @@
         <v>79</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>21</v>
@@ -10434,16 +10451,20 @@
         <v>90</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>546</v>
+        <v>284</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>547</v>
+        <v>540</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
+        <v>541</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>543</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>21</v>
       </c>
@@ -10467,13 +10488,13 @@
         <v>21</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>21</v>
+        <v>209</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>21</v>
+        <v>544</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>21</v>
+        <v>545</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>21</v>
@@ -10491,13 +10512,13 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>21</v>
@@ -10512,21 +10533,21 @@
         <v>21</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>21</v>
+        <v>547</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
-    <row r="69" hidden="true">
+    <row r="69">
       <c r="A69" t="s" s="2">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10537,25 +10558,25 @@
         <v>79</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>103</v>
+        <v>550</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>104</v>
+        <v>551</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>105</v>
+        <v>552</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10606,19 +10627,19 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>106</v>
+        <v>553</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>21</v>
+        <v>101</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>21</v>
@@ -10627,32 +10648,32 @@
         <v>21</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>21</v>
+        <v>554</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>109</v>
+        <v>21</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>21</v>
@@ -10664,17 +10685,15 @@
         <v>21</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>21</v>
@@ -10711,31 +10730,31 @@
         <v>21</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>115</v>
+        <v>21</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>118</v>
+        <v>21</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>21</v>
@@ -10755,21 +10774,21 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>21</v>
+        <v>109</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>21</v>
@@ -10778,21 +10797,21 @@
         <v>21</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>284</v>
+        <v>110</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>554</v>
+        <v>111</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="N71" s="2"/>
-      <c r="O71" t="s" s="2">
-        <v>556</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>21</v>
       </c>
@@ -10816,43 +10835,43 @@
         <v>21</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>209</v>
+        <v>21</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>557</v>
+        <v>21</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>558</v>
+        <v>21</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB71" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AC71" t="s" s="2">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="AD71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>559</v>
+        <v>117</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>21</v>
@@ -10861,21 +10880,21 @@
         <v>21</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>560</v>
+        <v>21</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10898,19 +10917,17 @@
         <v>90</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>562</v>
+        <v>284</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>565</v>
-      </c>
+        <v>559</v>
+      </c>
+      <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>21</v>
@@ -10935,13 +10952,13 @@
         <v>21</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>21</v>
+        <v>209</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>21</v>
+        <v>561</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>21</v>
+        <v>562</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>21</v>
@@ -10959,7 +10976,7 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10980,21 +10997,21 @@
         <v>21</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>543</v>
+        <v>21</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>568</v>
+        <v>564</v>
       </c>
     </row>
-    <row r="73" hidden="true">
+    <row r="73">
       <c r="A73" t="s" s="2">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11008,7 +11025,7 @@
         <v>89</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>21</v>
@@ -11017,19 +11034,19 @@
         <v>90</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="O73" t="s" s="2">
         <v>570</v>
-      </c>
-      <c r="L73" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>574</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>21</v>
@@ -11054,13 +11071,11 @@
         <v>21</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>21</v>
+        <v>571</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>21</v>
@@ -11078,7 +11093,7 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -11099,21 +11114,21 @@
         <v>21</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>576</v>
+        <v>547</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>577</v>
+        <v>573</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11136,19 +11151,19 @@
         <v>90</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="O74" t="s" s="2">
         <v>579</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>583</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>21</v>
@@ -11197,7 +11212,7 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -11218,21 +11233,21 @@
         <v>21</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>586</v>
+        <v>582</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11255,19 +11270,19 @@
         <v>90</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="O75" t="s" s="2">
         <v>588</v>
-      </c>
-      <c r="L75" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>592</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>21</v>
@@ -11316,7 +11331,7 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -11337,21 +11352,21 @@
         <v>21</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>21</v>
+        <v>591</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11374,17 +11389,19 @@
         <v>90</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="N76" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="O76" t="s" s="2">
         <v>597</v>
-      </c>
-      <c r="N76" s="2"/>
-      <c r="O76" t="s" s="2">
-        <v>598</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>21</v>
@@ -11433,7 +11450,7 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -11454,7 +11471,7 @@
         <v>21</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>21</v>
@@ -11488,19 +11505,21 @@
         <v>21</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="K77" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="L77" t="s" s="2">
         <v>601</v>
       </c>
-      <c r="L77" t="s" s="2">
+      <c r="M77" t="s" s="2">
         <v>602</v>
       </c>
-      <c r="M77" t="s" s="2">
+      <c r="N77" s="2"/>
+      <c r="O77" t="s" s="2">
         <v>603</v>
       </c>
-      <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>21</v>
       </c>
@@ -11548,7 +11567,7 @@
         <v>21</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -11566,24 +11585,24 @@
         <v>21</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>604</v>
+        <v>21</v>
       </c>
       <c r="AM77" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO77" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="2">
         <v>605</v>
       </c>
-      <c r="AN77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO77" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="78" hidden="true">
-      <c r="A78" t="s" s="2">
-        <v>606</v>
-      </c>
       <c r="B78" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11597,7 +11616,7 @@
         <v>89</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>21</v>
@@ -11606,13 +11625,13 @@
         <v>21</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>103</v>
+        <v>606</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>104</v>
+        <v>607</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>105</v>
+        <v>608</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11663,7 +11682,7 @@
         <v>21</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>106</v>
+        <v>605</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11675,16 +11694,16 @@
         <v>21</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>21</v>
+        <v>101</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>21</v>
+        <v>609</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>107</v>
+        <v>610</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>21</v>
@@ -11695,21 +11714,21 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>109</v>
+        <v>21</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>21</v>
@@ -11721,17 +11740,15 @@
         <v>21</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>21</v>
@@ -11780,19 +11797,19 @@
         <v>21</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>118</v>
+        <v>21</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>21</v>
@@ -11812,14 +11829,14 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>467</v>
+        <v>109</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -11832,26 +11849,24 @@
         <v>21</v>
       </c>
       <c r="I80" t="s" s="2">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="K80" t="s" s="2">
         <v>110</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>468</v>
+        <v>111</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>469</v>
+        <v>112</v>
       </c>
       <c r="N80" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="O80" t="s" s="2">
-        <v>260</v>
-      </c>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>21</v>
       </c>
@@ -11899,7 +11914,7 @@
         <v>21</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>470</v>
+        <v>117</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11920,7 +11935,7 @@
         <v>21</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>241</v>
+        <v>107</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>21</v>
@@ -11931,44 +11946,46 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>21</v>
+        <v>471</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I81" t="s" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>601</v>
+        <v>110</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>610</v>
+        <v>472</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>611</v>
+        <v>473</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="O81" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="O81" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="P81" t="s" s="2">
         <v>21</v>
       </c>
@@ -12016,19 +12033,19 @@
         <v>21</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>609</v>
+        <v>474</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>21</v>
@@ -12037,7 +12054,7 @@
         <v>21</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>613</v>
+        <v>241</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>21</v>
@@ -12074,15 +12091,17 @@
         <v>21</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>103</v>
+        <v>606</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>104</v>
+        <v>615</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N82" s="2"/>
+        <v>616</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>617</v>
+      </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>21</v>
@@ -12131,7 +12150,7 @@
         <v>21</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>106</v>
+        <v>614</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -12143,7 +12162,7 @@
         <v>21</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>21</v>
+        <v>101</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>21</v>
@@ -12152,7 +12171,7 @@
         <v>21</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>107</v>
+        <v>618</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>21</v>
@@ -12163,21 +12182,21 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>109</v>
+        <v>21</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>21</v>
@@ -12189,17 +12208,15 @@
         <v>21</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N83" s="2"/>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>21</v>
@@ -12248,19 +12265,19 @@
         <v>21</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>118</v>
+        <v>21</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>21</v>
@@ -12280,14 +12297,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>467</v>
+        <v>109</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -12300,26 +12317,24 @@
         <v>21</v>
       </c>
       <c r="I84" t="s" s="2">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="K84" t="s" s="2">
         <v>110</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>468</v>
+        <v>111</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>469</v>
+        <v>112</v>
       </c>
       <c r="N84" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="O84" t="s" s="2">
-        <v>260</v>
-      </c>
+      <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>21</v>
       </c>
@@ -12367,7 +12382,7 @@
         <v>21</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>470</v>
+        <v>117</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -12388,7 +12403,7 @@
         <v>21</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>241</v>
+        <v>107</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>21</v>
@@ -12399,42 +12414,46 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>21</v>
+        <v>471</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I85" t="s" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>588</v>
+        <v>110</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>618</v>
+        <v>472</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="N85" s="2"/>
-      <c r="O85" s="2"/>
+        <v>473</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="P85" t="s" s="2">
         <v>21</v>
       </c>
@@ -12482,19 +12501,19 @@
         <v>21</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>617</v>
+        <v>474</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>21</v>
@@ -12503,7 +12522,7 @@
         <v>21</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>620</v>
+        <v>241</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>21</v>
@@ -12514,10 +12533,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12540,7 +12559,7 @@
         <v>21</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>622</v>
+        <v>593</v>
       </c>
       <c r="L86" t="s" s="2">
         <v>623</v>
@@ -12597,7 +12616,7 @@
         <v>21</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -12655,13 +12674,13 @@
         <v>21</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12733,7 +12752,7 @@
         <v>21</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>21</v>
@@ -12744,10 +12763,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12770,20 +12789,16 @@
         <v>21</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="N88" t="s" s="2">
         <v>633</v>
       </c>
-      <c r="O88" t="s" s="2">
-        <v>634</v>
-      </c>
+      <c r="N88" s="2"/>
+      <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>21</v>
       </c>
@@ -12831,7 +12846,7 @@
         <v>21</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -12849,10 +12864,10 @@
         <v>21</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>635</v>
+        <v>21</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>21</v>
@@ -12863,10 +12878,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12889,18 +12904,20 @@
         <v>21</v>
       </c>
       <c r="K89" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="N89" t="s" s="2">
         <v>638</v>
       </c>
-      <c r="L89" t="s" s="2">
+      <c r="O89" t="s" s="2">
         <v>639</v>
       </c>
-      <c r="M89" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>21</v>
       </c>
@@ -12948,7 +12965,7 @@
         <v>21</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -12966,24 +12983,24 @@
         <v>21</v>
       </c>
       <c r="AL89" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="AN89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO89" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="2">
         <v>642</v>
       </c>
-      <c r="AM89" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="AN89" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO89" t="s" s="2">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="90" hidden="true">
-      <c r="A90" t="s" s="2">
-        <v>645</v>
-      </c>
       <c r="B90" t="s" s="2">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12997,7 +13014,7 @@
         <v>89</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>21</v>
@@ -13006,15 +13023,17 @@
         <v>21</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>588</v>
+        <v>643</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="N90" t="s" s="2">
         <v>646</v>
       </c>
-      <c r="M90" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="N90" s="2"/>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>21</v>
@@ -13063,7 +13082,7 @@
         <v>21</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -13081,24 +13100,24 @@
         <v>21</v>
       </c>
       <c r="AL90" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="AM90" t="s" s="2">
         <v>648</v>
       </c>
-      <c r="AM90" t="s" s="2">
+      <c r="AN90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO90" t="s" s="2">
         <v>649</v>
       </c>
-      <c r="AN90" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO90" t="s" s="2">
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="2">
         <v>650</v>
       </c>
-    </row>
-    <row r="91" hidden="true">
-      <c r="A91" t="s" s="2">
-        <v>651</v>
-      </c>
       <c r="B91" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13112,7 +13131,7 @@
         <v>89</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>21</v>
@@ -13121,17 +13140,15 @@
         <v>21</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>622</v>
+        <v>593</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>652</v>
       </c>
-      <c r="M91" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>654</v>
-      </c>
+      <c r="N91" s="2"/>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>21</v>
@@ -13180,7 +13197,7 @@
         <v>21</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -13198,24 +13215,24 @@
         <v>21</v>
       </c>
       <c r="AL91" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO91" t="s" s="2">
         <v>655</v>
-      </c>
-      <c r="AM91" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="AN91" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO91" t="s" s="2">
-        <v>21</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13238,15 +13255,17 @@
         <v>21</v>
       </c>
       <c r="K92" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>658</v>
       </c>
-      <c r="L92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>659</v>
       </c>
-      <c r="M92" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="N92" s="2"/>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>21</v>
@@ -13295,7 +13314,7 @@
         <v>21</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -13313,13 +13332,13 @@
         <v>21</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>21</v>
+        <v>660</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>661</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>398</v>
+        <v>21</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>21</v>
@@ -13353,13 +13372,13 @@
         <v>21</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>601</v>
+        <v>663</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13428,13 +13447,13 @@
         <v>21</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>665</v>
+        <v>21</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>666</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>21</v>
+        <v>402</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>21</v>
@@ -13468,13 +13487,13 @@
         <v>21</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>103</v>
+        <v>606</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>104</v>
+        <v>668</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>105</v>
+        <v>669</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13525,7 +13544,7 @@
         <v>21</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>106</v>
+        <v>667</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -13537,16 +13556,16 @@
         <v>21</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>21</v>
+        <v>101</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>21</v>
+        <v>670</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>107</v>
+        <v>671</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>21</v>
@@ -13557,21 +13576,21 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>109</v>
+        <v>21</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>21</v>
@@ -13583,17 +13602,15 @@
         <v>21</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N95" s="2"/>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>21</v>
@@ -13642,19 +13659,19 @@
         <v>21</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>118</v>
+        <v>21</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>21</v>
@@ -13674,14 +13691,14 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>467</v>
+        <v>109</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -13694,26 +13711,24 @@
         <v>21</v>
       </c>
       <c r="I96" t="s" s="2">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="K96" t="s" s="2">
         <v>110</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>468</v>
+        <v>111</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>469</v>
+        <v>112</v>
       </c>
       <c r="N96" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="O96" t="s" s="2">
-        <v>260</v>
-      </c>
+      <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>21</v>
       </c>
@@ -13761,7 +13776,7 @@
         <v>21</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>470</v>
+        <v>117</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -13782,7 +13797,7 @@
         <v>21</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>241</v>
+        <v>107</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>21</v>
@@ -13793,44 +13808,46 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>21</v>
+        <v>471</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I97" t="s" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>507</v>
+        <v>110</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>671</v>
+        <v>472</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>672</v>
+        <v>473</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>673</v>
-      </c>
-      <c r="O97" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="O97" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="P97" t="s" s="2">
         <v>21</v>
       </c>
@@ -13854,13 +13871,13 @@
         <v>21</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>209</v>
+        <v>21</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>674</v>
+        <v>21</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>675</v>
+        <v>21</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>21</v>
@@ -13878,42 +13895,42 @@
         <v>21</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>670</v>
+        <v>474</v>
       </c>
       <c r="AG97" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>665</v>
+        <v>21</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>676</v>
+        <v>241</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>677</v>
+        <v>21</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13921,7 +13938,7 @@
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G98" t="s" s="2">
         <v>89</v>
@@ -13936,15 +13953,17 @@
         <v>21</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>284</v>
+        <v>511</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>680</v>
-      </c>
-      <c r="N98" s="2"/>
+        <v>677</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>678</v>
+      </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>21</v>
@@ -13972,10 +13991,10 @@
         <v>209</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>21</v>
@@ -13993,10 +14012,10 @@
         <v>21</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="AG98" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH98" t="s" s="2">
         <v>89</v>
@@ -14011,24 +14030,24 @@
         <v>21</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>683</v>
+        <v>670</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>685</v>
+        <v>682</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14051,13 +14070,13 @@
         <v>21</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>687</v>
+        <v>284</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -14084,13 +14103,13 @@
         <v>21</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>21</v>
+        <v>209</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>21</v>
+        <v>686</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>21</v>
+        <v>687</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>21</v>
@@ -14108,7 +14127,7 @@
         <v>21</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -14123,38 +14142,38 @@
         <v>101</v>
       </c>
       <c r="AK99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO99" t="s" s="2">
         <v>690</v>
-      </c>
-      <c r="AL99" t="s" s="2">
-        <v>683</v>
-      </c>
-      <c r="AM99" t="s" s="2">
-        <v>691</v>
-      </c>
-      <c r="AN99" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO99" t="s" s="2">
-        <v>21</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>693</v>
+        <v>21</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>21</v>
@@ -14166,17 +14185,15 @@
         <v>21</v>
       </c>
       <c r="K100" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>694</v>
       </c>
-      <c r="L100" t="s" s="2">
-        <v>695</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>696</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>697</v>
-      </c>
+      <c r="N100" s="2"/>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>21</v>
@@ -14225,13 +14242,13 @@
         <v>21</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>21</v>
@@ -14240,13 +14257,13 @@
         <v>101</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>21</v>
+        <v>695</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>21</v>
+        <v>688</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>21</v>
@@ -14257,14 +14274,14 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>21</v>
+        <v>698</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -14283,16 +14300,16 @@
         <v>21</v>
       </c>
       <c r="K101" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="L101" t="s" s="2">
         <v>700</v>
       </c>
-      <c r="L101" t="s" s="2">
+      <c r="M101" t="s" s="2">
         <v>701</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="N101" t="s" s="2">
         <v>702</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>703</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14342,7 +14359,7 @@
         <v>21</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -14357,23 +14374,140 @@
         <v>101</v>
       </c>
       <c r="AK101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="AN101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO101" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="102" hidden="true">
+      <c r="A102" t="s" s="2">
         <v>704</v>
       </c>
-      <c r="AL101" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM101" t="s" s="2">
+      <c r="B102" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E102" s="2"/>
+      <c r="F102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K102" t="s" s="2">
         <v>705</v>
       </c>
-      <c r="AN101" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO101" t="s" s="2">
+      <c r="L102" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="O102" s="2"/>
+      <c r="P102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q102" s="2"/>
+      <c r="R102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF102" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="AG102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ102" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK102" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="AN102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO102" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO101">
+  <autoFilter ref="A1:AO102">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -14383,7 +14517,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI100">
+  <conditionalFormatting sqref="A2:AI101">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
